--- a/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F14" t="n">
         <v>30</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F33" t="n">
         <v>61</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L33" t="n">
         <v>13</v>

--- a/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1639,7 +1639,7 @@
         <v>56</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>68</v>
@@ -2445,7 +2445,7 @@
         <v>69</v>
       </c>
       <c r="F33" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
         <v>82</v>

--- a/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
@@ -659,10 +659,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -721,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -771,7 +771,7 @@
         <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1651,10 +1651,10 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L20" t="n">
         <v>12</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
         <v>18</v>
@@ -2023,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L26" t="n">
         <v>21</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2147,10 +2147,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="L28" t="n">
         <v>13</v>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 31/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -892,10 +892,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -910,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>40</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F18" t="n">
         <v>63</v>
@@ -1527,10 +1527,10 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -2135,7 +2135,7 @@
         <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
         <v>78</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" t="n">
         <v>62</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L33" t="n">
         <v>14</v>
